--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486678_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486678_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7922</v>
+        <v>7.5632</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2472</v>
+        <v>5.8195</v>
       </c>
       <c r="F2" t="n">
-        <v>1.545</v>
+        <v>1.7437</v>
       </c>
       <c r="G2" t="n">
         <v>5.9605</v>
@@ -610,13 +610,13 @@
         <v>1.9308</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4193</v>
+        <v>0.3517</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9657</v>
+        <v>-0.3935</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5465</v>
+        <v>0.7451</v>
       </c>
       <c r="V2" t="n">
         <v>0.2856</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4831</v>
+        <v>6.2225</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6562</v>
+        <v>4.346</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8269</v>
+        <v>1.8766</v>
       </c>
       <c r="G3" t="n">
         <v>3.1387</v>
@@ -688,13 +688,13 @@
         <v>1.5446</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5295</v>
+        <v>0.2689</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4411</v>
+        <v>0.1308</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.1381</v>
       </c>
       <c r="V3" t="n">
         <v>1.2703</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>P. ROBLES LLANOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2694</v>
+        <v>4.6363</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1023</v>
+        <v>0.1672</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1671</v>
+        <v>4.4691</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7787</v>
+        <v>-1.0023</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9378</v>
+        <v>0.0964</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8409</v>
+        <v>-1.0987</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1661</v>
+        <v>-2.1252</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3523</v>
+        <v>-0.1788</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8138</v>
+        <v>-1.9464</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3874</v>
+        <v>1.1228</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4145</v>
+        <v>0.2752</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0271</v>
+        <v>0.8477</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.7377</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9308</v>
+        <v>1.7377</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9195</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2958</v>
+        <v>-0.4486</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6237</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5712</v>
+        <v>3.3975</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5712</v>
+        <v>2.741</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. ROBLES LLANOS</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1882</v>
+        <v>4.336</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4051</v>
+        <v>2.0199</v>
       </c>
       <c r="F5" t="n">
-        <v>4.5933</v>
+        <v>2.3161</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0023</v>
+        <v>2.7787</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0964</v>
+        <v>1.9378</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0987</v>
+        <v>0.8409</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.1252</v>
+        <v>3.1661</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1788</v>
+        <v>2.3523</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.9464</v>
+        <v>0.8138</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1228</v>
+        <v>-0.3874</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2752</v>
+        <v>-0.4145</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8477</v>
+        <v>0.0271</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7377</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7377</v>
+        <v>1.9308</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0554</v>
+        <v>0.986</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0209</v>
+        <v>0.2133</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0763</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>3.3975</v>
+        <v>0.5712</v>
       </c>
       <c r="W5" t="n">
-        <v>2.741</v>
+        <v>0.5712</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.283</v>
+        <v>0.439</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3458</v>
+        <v>-0.2748</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9372</v>
+        <v>0.7138</v>
       </c>
       <c r="G6" t="n">
         <v>1.2184</v>
@@ -922,13 +922,13 @@
         <v>1.3515</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2577</v>
+        <v>0.4137</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8547</v>
+        <v>0.2341</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4031</v>
+        <v>0.1796</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6138</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0148</v>
+        <v>0.0267</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.135</v>
+        <v>-1.3419</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1203</v>
+        <v>1.3686</v>
       </c>
       <c r="G7" t="n">
         <v>-1.9497</v>
@@ -1000,13 +1000,13 @@
         <v>1.1585</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1655</v>
+        <v>-0.1241</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2486</v>
+        <v>-0.4555</v>
       </c>
       <c r="U7" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.3314</v>
       </c>
       <c r="V7" t="n">
         <v>0.9421</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2151</v>
+        <v>-0.1862</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.91</v>
+        <v>-0.8066</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6949</v>
+        <v>0.6204</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7171</v>
@@ -1078,13 +1078,13 @@
         <v>0.1931</v>
       </c>
       <c r="S8" t="n">
-        <v>0.309</v>
+        <v>0.3379</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1932</v>
+        <v>-0.0898</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5022</v>
+        <v>0.4277</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5959</v>
+        <v>-0.4346</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2477</v>
+        <v>-1.9374</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6518</v>
+        <v>1.5028</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9379999999999999</v>
@@ -1156,13 +1156,13 @@
         <v>1.3515</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.044</v>
+        <v>0.1172</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3312</v>
+        <v>-0.0209</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2872</v>
+        <v>0.1382</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0029</v>
+        <v>-0.8857</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1716</v>
+        <v>-2.8062</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1688</v>
+        <v>1.9204</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6817</v>
@@ -1234,13 +1234,13 @@
         <v>2.1239</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5517</v>
+        <v>0.6688</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5244</v>
+        <v>-0.159</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0761</v>
+        <v>0.8278</v>
       </c>
       <c r="V10" t="n">
         <v>0.8995</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5057</v>
+        <v>-1.3278</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8787</v>
+        <v>-1.7753</v>
       </c>
       <c r="F11" t="n">
-        <v>0.373</v>
+        <v>0.4475</v>
       </c>
       <c r="G11" t="n">
         <v>-0.0108</v>
@@ -1312,13 +1312,13 @@
         <v>1.3515</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0497</v>
+        <v>0.2276</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1652</v>
+        <v>0.2686</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1155</v>
+        <v>-0.041</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5602</v>
+        <v>-2.992</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0228</v>
+        <v>-2.5539</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5374</v>
+        <v>-0.4381</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6582</v>
@@ -1390,13 +1390,13 @@
         <v>1.7377</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.458</v>
+        <v>0.1102</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4416</v>
+        <v>0.0273</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0164</v>
+        <v>0.083</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2856</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>17.1213</v>
+        <v>17.3974</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5806000000000004</v>
+        <v>0.8564999999999987</v>
       </c>
       <c r="F13" t="n">
         <v>16.5409</v>
@@ -1468,10 +1468,10 @@
         <v>16.4116</v>
       </c>
       <c r="S13" t="n">
-        <v>3.585699999999999</v>
+        <v>3.8614</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9687999999999997</v>
+        <v>-0.6932000000000001</v>
       </c>
       <c r="U13" t="n">
         <v>4.5547</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4436</v>
+        <v>2.296</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1309</v>
+        <v>0.8206</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3127</v>
+        <v>1.4755</v>
       </c>
       <c r="G14" t="n">
         <v>0.8549</v>
@@ -1546,13 +1546,13 @@
         <v>1.1585</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4302</v>
+        <v>0.2827</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5515</v>
+        <v>0.2412</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1212</v>
+        <v>0.0415</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8008</v>
+        <v>2.1759</v>
       </c>
       <c r="E15" t="n">
         <v>0.8679</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9329</v>
+        <v>1.308</v>
       </c>
       <c r="G15" t="n">
         <v>1.5638</v>
@@ -1624,13 +1624,13 @@
         <v>0.9654</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4854</v>
+        <v>-0.1102</v>
       </c>
       <c r="T15" t="n">
         <v>-0.5518</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0665</v>
+        <v>0.4416</v>
       </c>
       <c r="V15" t="n">
         <v>-0.243</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. FORTES SILVA</t>
+          <t>J. SANTOLARIA MARTIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3849</v>
+        <v>0.5198</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.3617</v>
+        <v>-0.535</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7466</v>
+        <v>1.0549</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3962</v>
+        <v>0.5888</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0954</v>
+        <v>0.0689</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3008</v>
+        <v>0.5199</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6603</v>
+        <v>-0.0384</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4568</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2035</v>
+        <v>-0.0384</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0564</v>
+        <v>0.6272</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5522</v>
+        <v>0.0689</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5042</v>
+        <v>0.5583</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1931</v>
+        <v>0.3862</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1239</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9308</v>
+        <v>0.3862</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4029</v>
+        <v>-0.4551</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4693</v>
+        <v>-0.4966</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8722</v>
+        <v>0.0415</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. SANTOLARIA MARTIN</t>
+          <t>S. GUTIERREZ ROA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3571</v>
+        <v>0.0317</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.535</v>
+        <v>0.3704</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8922</v>
+        <v>-0.3387</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5888</v>
+        <v>1.2539</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0689</v>
+        <v>-0.8417</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5199</v>
+        <v>2.0956</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0384</v>
+        <v>1.3856</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.1242</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0384</v>
+        <v>1.2615</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6272</v>
+        <v>-0.1318</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0689</v>
+        <v>-0.9659</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5583</v>
+        <v>0.8341</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3862</v>
+        <v>1.1585</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3862</v>
+        <v>1.1585</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6179</v>
+        <v>-0.4965</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4966</v>
+        <v>-0.3587</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1212</v>
+        <v>-0.1377</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.8842</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. GUTIERREZ ROA</t>
+          <t>A. FORTES SILVA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6303</v>
+        <v>-0.0317</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3704</v>
+        <v>-1.5686</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0007</v>
+        <v>1.5368</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2539</v>
+        <v>-0.3962</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8417</v>
+        <v>-0.0954</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0956</v>
+        <v>-0.3008</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3856</v>
+        <v>0.6603</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1242</v>
+        <v>0.4568</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2615</v>
+        <v>0.2035</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1318</v>
+        <v>-1.0564</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9659</v>
+        <v>-0.5522</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8341</v>
+        <v>-0.5042</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1585</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.1239</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1585</v>
+        <v>1.9308</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1585</v>
+        <v>-0.0137</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3587</v>
+        <v>-0.6762</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7997</v>
+        <v>0.6625</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.8842</v>
+        <v>0.5712</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6565</v>
+        <v>0.5712</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2785</v>
+        <v>-0.9987</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.5286</v>
+        <v>-3.4252</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2501</v>
+        <v>2.4266</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6057</v>
@@ -1936,13 +1936,13 @@
         <v>1.5446</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0936</v>
+        <v>0.1863</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9106</v>
+        <v>-0.8071</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8169</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Í. MATEO CASTAÑO</t>
+          <t>G. CAMPOS MARCOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0761</v>
+        <v>-1.7392</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6219</v>
+        <v>-2.0771</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.698</v>
+        <v>0.3379</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2426</v>
+        <v>1.0939</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6555</v>
+        <v>-1.6551</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4129</v>
+        <v>2.749</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4346</v>
+        <v>2.4469</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4826</v>
+        <v>0.0008</v>
       </c>
       <c r="L20" t="n">
-        <v>1.9171</v>
+        <v>2.4461</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6772</v>
+        <v>-1.353</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.173</v>
+        <v>-1.6558</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5042</v>
+        <v>0.3029</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3515</v>
+        <v>-1.9308</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-4.0546</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3515</v>
+        <v>2.1239</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3587</v>
+        <v>-0.3311</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4418</v>
+        <v>-0.4693</v>
       </c>
       <c r="U20" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.1383</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.8262</v>
+        <v>-0.5712</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3709</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4554</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. CAMPOS MARCOS</t>
+          <t>Í. MATEO CASTAÑO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7267</v>
+        <v>-1.8278</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4908</v>
+        <v>0.6219</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2359</v>
+        <v>-2.4496</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0939</v>
+        <v>-0.2426</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6551</v>
+        <v>-1.6555</v>
       </c>
       <c r="I21" t="n">
-        <v>2.749</v>
+        <v>1.4129</v>
       </c>
       <c r="J21" t="n">
-        <v>2.4469</v>
+        <v>1.4346</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0008</v>
+        <v>-0.4826</v>
       </c>
       <c r="L21" t="n">
-        <v>2.4461</v>
+        <v>1.9171</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.353</v>
+        <v>-1.6772</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6558</v>
+        <v>-1.173</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3029</v>
+        <v>-0.5042</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.9308</v>
+        <v>1.3515</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.0546</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1239</v>
+        <v>1.3515</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3186</v>
+        <v>-0.1104</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.883</v>
+        <v>-0.4418</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4355</v>
+        <v>0.3314</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5712</v>
+        <v>-2.8262</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.3709</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5712</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0429</v>
+        <v>-2.7685</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.289</v>
+        <v>-1.9788</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7539</v>
+        <v>-0.7897999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6832</v>
@@ -2170,13 +2170,13 @@
         <v>0.7723</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5295</v>
+        <v>-0.2551</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8277</v>
+        <v>-0.5175</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2983</v>
+        <v>0.2624</v>
       </c>
       <c r="V22" t="n">
         <v>0.3282</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1599</v>
+        <v>-3.0854</v>
       </c>
       <c r="E23" t="n">
         <v>-2.1167</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0432</v>
+        <v>-0.9687</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9585</v>
@@ -2248,13 +2248,13 @@
         <v>0.5792</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7228</v>
+        <v>-0.6483</v>
       </c>
       <c r="T23" t="n">
         <v>-0.5518</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1709</v>
+        <v>-0.0965</v>
       </c>
       <c r="V23" t="n">
         <v>-0.8995</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7987</v>
+        <v>-4.2057</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2809</v>
+        <v>-3.5911</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5179</v>
+        <v>-0.6146</v>
       </c>
       <c r="G24" t="n">
         <v>-2.774</v>
@@ -2326,13 +2326,13 @@
         <v>1.1585</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6897</v>
+        <v>0.2827</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2479</v>
+        <v>-0.0624</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4418</v>
+        <v>0.3451</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9421</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.3948</v>
+        <v>-5.4196</v>
       </c>
       <c r="E25" t="n">
         <v>-3.9292</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4656</v>
+        <v>-1.4904</v>
       </c>
       <c r="G25" t="n">
         <v>-3.8335</v>
@@ -2404,13 +2404,13 @@
         <v>1.3515</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1764</v>
+        <v>0.1516</v>
       </c>
       <c r="T25" t="n">
         <v>0.1375</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0389</v>
+        <v>0.014</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-17.1215</v>
+        <v>-15.0532</v>
       </c>
       <c r="E26" t="n">
-        <v>-16.5408</v>
+        <v>-16.5409</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.5807000000000002</v>
+        <v>1.4879</v>
       </c>
       <c r="G26" t="n">
         <v>-5.1384</v>
@@ -2452,7 +2452,7 @@
         <v>-7.240499999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>2.102100000000001</v>
+        <v>2.102099999999999</v>
       </c>
       <c r="J26" t="n">
         <v>4.595900000000001</v>
@@ -2482,19 +2482,19 @@
         <v>14.4809</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.5858</v>
+        <v>-1.5171</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.5544</v>
+        <v>-4.5545</v>
       </c>
       <c r="U26" t="n">
-        <v>0.9692000000000001</v>
+        <v>3.0375</v>
       </c>
       <c r="V26" t="n">
         <v>-6.4668</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.1706</v>
+        <v>-0.1705999999999999</v>
       </c>
       <c r="X26" t="n">
         <v>-6.2963</v>
